--- a/school_surveys/010_high_school_student_climate_change_awareness_survey--school_surveys.xlsx
+++ b/school_surveys/010_high_school_student_climate_change_awareness_survey--school_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,15 +520,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>school_surveys_title</t>
+          <t>school_surveys_page_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>High School Student Climate Change Awareness Survey</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Introduction</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please answer the questions honestly</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -543,12 +547,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>school_surveys_category</t>
+          <t>school_surveys_q1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>What is your favorite subject in school?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +570,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>school_surveys_description</t>
+          <t>school_surveys_q2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Have you learned about climate change in school?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,18 +593,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>school_surveys_form_id</t>
+          <t>school_surveys_q3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Form ID</t>
+          <t>Can you list three main causes of climate change?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,35 +616,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>school_surveys_assigned_tool</t>
+          <t>school_surveys_q4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Assigned Tool</t>
+          <t>What are some effects of climate change that you've noticed in your community?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>school_surveys_output_file</t>
+          <t>school_surveys_q5</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Output File</t>
+          <t>Do you think humans are responsible for climate change?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +657,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>school_surveys_category_2</t>
+          <t>school_surveys_q6</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Can you describe a personal experience related to climate change?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +685,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>school_surveys_description_2</t>
+          <t>school_surveys_q7</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>What are some ways to reduce your carbon footprint?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +703,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>school_surveys_form_id_2</t>
+          <t>school_surveys_q8</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Form ID</t>
+          <t>Do you think climate change is a serious issue that requires immediate action?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +731,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>school_surveys_assigned_tool_2</t>
+          <t>school_surveys_q9</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Assigned Tool</t>
+          <t>Can you name one climate change-related policy or law that you think is effective?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +754,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>school_surveys_output_file_2</t>
+          <t>school_surveys_q10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Output File</t>
+          <t>What are some climate change-related concerns you have for your community's future?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +777,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>school_surveys_title_2</t>
+          <t>school_surveys_q11</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>TITLE</t>
+          <t>Can you suggest a way to educate others about climate change?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,292 +800,16 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>school_surveys_category_3</t>
+          <t>school_surveys_q12</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CATEGORY</t>
+          <t>Do you think climate change has impacted your daily life?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>school_surveys_description_3</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>DESCRIPTION</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>school_surveys_form_id_3</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>FORM_ID</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>school_surveys_assigned_tool_3</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>ASSIGNED_TOOL</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>school_surveys_output_file_3</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>OUTPUT_FILE</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>school_surveys_title_3</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>TITLE</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>school_surveys_category_4</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>CATEGORY</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>school_surveys_description_4</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>DESCRIPTION</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>school_surveys_form_id_4</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>FORM_ID</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>school_surveys_assigned_tool_4</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>ASSIGNED_TOOL</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>school_surveys_output_file_4</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>OUTPUT_FILE</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>school_surveys_title_4</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>TITLE</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>school_surveys_description_5</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>DESCRIPTION</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +826,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,136 +854,238 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>school_surveys_category_choices</t>
+          <t>school_surveys_q1_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>school_surveys</t>
+          <t>mathematics</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>School Surveys</t>
+          <t>Mathematics</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>school_surveys_category_choices</t>
+          <t>school_surveys_q1_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>science</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Science</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>school_surveys_category_2_choices</t>
+          <t>school_surveys_q1_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>school_surveys</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>School Surveys</t>
+          <t>English</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>school_surveys_category_2_choices</t>
+          <t>school_surveys_q1_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>arts</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Arts</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>school_surveys_category_3_choices</t>
+          <t>school_surveys_q1_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>school_surveys</t>
+          <t>physical_education</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>School Surveys</t>
+          <t>Physical Education</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>school_surveys_category_3_choices</t>
+          <t>school_surveys_q5_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>school_surveys_category_4_choices</t>
+          <t>school_surveys_q5_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>school_surveys</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>School Surveys</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>school_surveys_category_4_choices</t>
+          <t>school_surveys_q5_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>unsure</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Unsure</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>school_surveys_q8_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>school_surveys_q8_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>school_surveys_q8_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>unsure</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Unsure</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>school_surveys_q12_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>school_surveys_q12_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>school_surveys_q12_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>unsure</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Unsure</t>
         </is>
       </c>
     </row>
